--- a/testcase_new/reliability/java/S3暂时屏蔽用例记录表.xlsx
+++ b/testcase_new/reliability/java/S3暂时屏蔽用例记录表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>被屏蔽用例</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,10 +71,6 @@
   </si>
   <si>
     <t>PutRegionWithKillCoord17341</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-4845</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -531,7 +527,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -540,7 +536,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1"/>
     </row>
@@ -549,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1"/>
     </row>
@@ -567,7 +563,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1"/>
     </row>
@@ -576,7 +572,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1"/>
     </row>
@@ -585,7 +581,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1"/>
     </row>
